--- a/scripts/checks/results/HLR_results_08_>75_lg_families_noLgArea_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_08_>75_lg_families_noLgArea_tPBC.xlsx
@@ -553,66 +553,66 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>962</v>
+        <v>1182</v>
       </c>
       <c r="E2" t="n">
-        <v>960</v>
+        <v>1180</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3077269933674377</v>
+        <v>0.2430222915463953</v>
       </c>
       <c r="H2" t="n">
-        <v>426.7361442702318</v>
+        <v>378.8305795828101</v>
       </c>
       <c r="I2" t="n">
-        <v>9.971253084328792e-79</v>
+        <v>2.142744421722969e-73</v>
       </c>
       <c r="J2" t="n">
-        <v>110.0735669101074</v>
+        <v>138.3668153787242</v>
       </c>
       <c r="K2" t="n">
-        <v>159.0031185031185</v>
+        <v>182.7884940778342</v>
       </c>
       <c r="L2" t="n">
-        <v>48.92955159301106</v>
+        <v>44.42167869910998</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1146599655313619</v>
+        <v>0.1172600130328171</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1654558985464292</v>
+        <v>0.1547743387619256</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.7486643282984455, 'N1ratio-ArgsPreds': -0.2076128570460793}</t>
+          <t>{'const': 0.5838997183381505, 'N1ratio-ArgsPreds': -2.2076993978570845}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 3.609420076864592e-116, 'N1ratio-ArgsPreds': 9.971253084334582e-79}</t>
+          <t>{'const': 7.775219821683825e-118, 'N1ratio-ArgsPreds': 2.142744421721985e-73}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5547314605892099}</t>
+          <t>{'N1ratio-ArgsPreds': -0.49297291157465767}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5547314605892107)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.49297291157465845)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5547314605892106)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.49297291157465845)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(30.772699336743898)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(24.3022291546396)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -632,76 +632,76 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>962</v>
+        <v>1182</v>
       </c>
       <c r="E3" t="n">
-        <v>959</v>
+        <v>1179</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.309932915807294</v>
+        <v>0.243029434005724</v>
       </c>
       <c r="H3" t="n">
-        <v>215.3599795351147</v>
+        <v>189.2621163653774</v>
       </c>
       <c r="I3" t="n">
-        <v>5.602530738922377e-78</v>
+        <v>5.212741901581616e-72</v>
       </c>
       <c r="J3" t="n">
-        <v>109.7228183629943</v>
+        <v>138.3655098193395</v>
       </c>
       <c r="K3" t="n">
-        <v>159.0031185031185</v>
+        <v>182.7884940778342</v>
       </c>
       <c r="L3" t="n">
-        <v>24.64015007006211</v>
+        <v>22.21149212924733</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1144137834859169</v>
+        <v>0.1173583628662761</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1654558985464292</v>
+        <v>0.1547743387619256</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.7367253482977725, 'N1ratio-ArgsPreds': -0.2130532914365536, 'Fam_class': 0.0006058329789900769}</t>
+          <t>{'const': 0.5846789005586817, 'N1ratio-ArgsPreds': -2.2040046619576232, 'Fam_class': -2.8987753571532647e-05}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 1.0006382299714886e-108, 'N1ratio-ArgsPreds': 2.495655154958191e-76, 'Fam_class': 0.08028464407536798}</t>
+          <t>{'const': 9.50841278385966e-109, 'N1ratio-ArgsPreds': 1.1808755686741504e-67, 'Fam_class': 0.916018435400811}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5692680367849594, 'Fam_class': 0.04916537895054843}</t>
+          <t>{'N1ratio-ArgsPreds': -0.49214788769884166, 'Fam_class': -0.002796984756003274}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5477183770250377), 'Fam_class': np.float64(0.05644902179184039)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4754845360853714), 'Fam_class': np.float64(-0.0030717250736025897)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5438166849754508), 'Fam_class': np.float64(0.04696724858724697)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47025066037116536), 'Fam_class': np.float64(-0.00267253799384983)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(29.573658685768866), 'Fam_class': np.float64(0.22059224398562524)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.11356835795171), 'Fam_class': np.float64(0.0007142459328570874)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.002205922439856289</v>
+        <v>7.142459328646211e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>3.065614442829183</v>
+        <v>0.01112455348566031</v>
       </c>
       <c r="W3" t="n">
-        <v>0.08028464407538698</v>
+        <v>0.9160184354065133</v>
       </c>
     </row>
     <row r="4">
@@ -717,76 +717,76 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>962</v>
+        <v>1182</v>
       </c>
       <c r="E4" t="n">
-        <v>957</v>
+        <v>1177</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3354841239652072</v>
+        <v>0.277662385256643</v>
       </c>
       <c r="H4" t="n">
-        <v>120.7865448416666</v>
+        <v>113.1079916014004</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8926322900598e-83</v>
+        <v>1.214895712142636e-81</v>
       </c>
       <c r="J4" t="n">
-        <v>105.6600965843637</v>
+        <v>132.035004814713</v>
       </c>
       <c r="K4" t="n">
-        <v>159.0031185031185</v>
+        <v>182.7884940778342</v>
       </c>
       <c r="L4" t="n">
-        <v>13.33575547968869</v>
+        <v>12.6883723157803</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1104076244350718</v>
+        <v>0.1121792734194673</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1654558985464292</v>
+        <v>0.1547743387619256</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.7069103199539396, 'N1ratio-ArgsPreds': -0.19388770406769099, 'Fam_class': -5.4359048615197425e-05, 'Nlen_freq': -0.07524861491353746, 'Vlen_freq': 0.07848308204657117}</t>
+          <t>{'const': 0.5326382186273508, 'N1ratio-ArgsPreds': -1.977074929178288, 'Fam_class': -0.0007155067812620305, 'Nlen_freq': -0.7536569102315467, 'Vlen_freq': 1.1175476841519236}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 1.0700480337968409e-19, 'N1ratio-ArgsPreds': 3.0632702447460224e-62, 'Fam_class': 0.8791253206334037, 'Nlen_freq': 2.2368476768755657e-05, 'Vlen_freq': 2.2977887162960476e-09}</t>
+          <t>{'const': 1.582881953547104e-32, 'N1ratio-ArgsPreds': 4.685217924104467e-55, 'Fam_class': 0.01199021677031251, 'Nlen_freq': 2.6160414517557636e-06, 'Vlen_freq': 3.887777026105497e-13}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5180585191016708, 'Fam_class': -0.004411419181921493, 'Nlen_freq': -0.17791278714113695, 'Vlen_freq': 0.26324260184867804}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4414751325222649, 'Fam_class': -0.06903817348482645, 'Nlen_freq': -0.18807629279105129, 'Vlen_freq': 0.3047917757112661}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5015849446932864), 'Fam_class': np.float64(-0.0049172421393696136), 'Nlen_freq': np.float64(-0.13644853969357001), 'Vlen_freq': np.float64(0.19141279701137956)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.43297137096243027), 'Fam_class': np.float64(-0.07315028764011519), 'Nlen_freq': np.float64(-0.1363524484569532), 'Vlen_freq': np.float64(0.20929550802411598)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47263583254521935), 'Fam_class': np.float64(-0.004008478198378463), 'Nlen_freq': np.float64(-0.11228004390238101), 'Vlen_freq': np.float64(0.15897509305183943)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.40823294109963243), 'Fam_class': np.float64(-0.06233776402780797), 'Nlen_freq': np.float64(-0.1169790950076564), 'Vlen_freq': np.float64(0.18191005282583103)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.33846302057126), 'Fam_class': np.float64(0.001606789746687545), 'Nlen_freq': np.float64(1.2606808258720608), 'Vlen_freq': np.float64(2.527308021084101)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(16.665413419885596), 'Fam_class': np.float64(0.3885996823986669), 'Nlen_freq': np.float64(1.3684108668810302), 'Vlen_freq': np.float64(3.309126731909664)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.02555120815791323</v>
+        <v>0.03463295125091903</v>
       </c>
       <c r="V4" t="n">
-        <v>18.39873740341057</v>
+        <v>28.21601892960717</v>
       </c>
       <c r="W4" t="n">
-        <v>1.443186284729719e-08</v>
+        <v>1.073095963301676e-12</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_08_>75_lg_families_noLgArea_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_08_>75_lg_families_noLgArea_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2430222915463953</v>
+        <v>0.2355842238404511</v>
       </c>
       <c r="H2" t="n">
-        <v>378.8305795828101</v>
+        <v>363.662541775839</v>
       </c>
       <c r="I2" t="n">
-        <v>2.142744421722969e-73</v>
+        <v>6.968483886006474e-71</v>
       </c>
       <c r="J2" t="n">
-        <v>138.3668153787242</v>
+        <v>138.7796194903806</v>
       </c>
       <c r="K2" t="n">
-        <v>182.7884940778342</v>
+        <v>181.5499153976311</v>
       </c>
       <c r="L2" t="n">
-        <v>44.42167869910998</v>
+        <v>42.7702959072505</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1172600130328171</v>
+        <v>0.1176098470257463</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1547743387619256</v>
+        <v>0.1537255845873253</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.5838997183381505, 'N1ratio-ArgsPreds': -2.2076993978570845}</t>
+          <t>{'const': 0.5682328519626636, 'N1ratio-ArgsPreds': -2.118622554728008}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 7.775219821683825e-118, 'N1ratio-ArgsPreds': 2.142744421721985e-73}</t>
+          <t>{'const': 4.267556190895944e-115, 'N1ratio-ArgsPreds': 6.968483886004664e-71}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.49297291157465767}</t>
+          <t>{'N1ratio-ArgsPreds': -0.48537019257516306}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.49297291157465845)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.48537019257516234)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.49297291157465845)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4853701925751624)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(24.3022291546396)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(23.558422384045024)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.243029434005724</v>
+        <v>0.2357097723163037</v>
       </c>
       <c r="H3" t="n">
-        <v>189.2621163653774</v>
+        <v>181.8038563721716</v>
       </c>
       <c r="I3" t="n">
-        <v>5.212741901581616e-72</v>
+        <v>1.516253387259223e-69</v>
       </c>
       <c r="J3" t="n">
-        <v>138.3655098193395</v>
+        <v>138.7568261752113</v>
       </c>
       <c r="K3" t="n">
-        <v>182.7884940778342</v>
+        <v>181.5499153976311</v>
       </c>
       <c r="L3" t="n">
-        <v>22.21149212924733</v>
+        <v>21.39654461120992</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1173583628662761</v>
+        <v>0.117690268172359</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1547743387619256</v>
+        <v>0.1537255845873253</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.5846789005586817, 'N1ratio-ArgsPreds': -2.2040046619576232, 'Fam_class': -2.8987753571532647e-05}</t>
+          <t>{'const': 0.5715863027053953, 'N1ratio-ArgsPreds': -2.1038747852921906, 'Fam_class': -0.00012087906762604605}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 9.50841278385966e-109, 'N1ratio-ArgsPreds': 1.1808755686741504e-67, 'Fam_class': 0.916018435400811}</t>
+          <t>{'const': 3.187628831203141e-106, 'N1ratio-ArgsPreds': 5.885558436980357e-65, 'Fam_class': 0.6599584798021098}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.49214788769884166, 'Fam_class': -0.002796984756003274}</t>
+          <t>{'N1ratio-ArgsPreds': -0.48199152199736595, 'Fam_class': -0.011703157297484928}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4754845360853714), 'Fam_class': np.float64(-0.0030717250736025897)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4668105918264926), 'Fam_class': np.float64(-0.012815657774598577)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47025066037116536), 'Fam_class': np.float64(-0.00267253799384983)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46146851927307075), 'Fam_class': np.float64(-0.011204841625506699)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.11356835795171), 'Fam_class': np.float64(0.0007142459328570874)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.295319428008046), 'Fam_class': np.float64(0.012554847585268758)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>7.142459328646211e-06</v>
+        <v>0.0001255484758526659</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01112455348566031</v>
+        <v>0.1936720471736194</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9160184354065133</v>
+        <v>0.659958479806684</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.277662385256643</v>
+        <v>0.2735633506401258</v>
       </c>
       <c r="H4" t="n">
-        <v>113.1079916014004</v>
+        <v>110.8094091849427</v>
       </c>
       <c r="I4" t="n">
-        <v>1.214895712142636e-81</v>
+        <v>3.344779760471392e-80</v>
       </c>
       <c r="J4" t="n">
-        <v>132.035004814713</v>
+        <v>131.8845122330238</v>
       </c>
       <c r="K4" t="n">
-        <v>182.7884940778342</v>
+        <v>181.5499153976311</v>
       </c>
       <c r="L4" t="n">
-        <v>12.6883723157803</v>
+        <v>12.41635079115184</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1121792734194673</v>
+        <v>0.1120514122625521</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1547743387619256</v>
+        <v>0.1537255845873253</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.5326382186273508, 'N1ratio-ArgsPreds': -1.977074929178288, 'Fam_class': -0.0007155067812620305, 'Nlen_freq': -0.7536569102315467, 'Vlen_freq': 1.1175476841519236}</t>
+          <t>{'const': 0.5318082685667341, 'N1ratio-ArgsPreds': -1.8790716772582738, 'Fam_class': -0.0008153377416659804, 'Nlen_freq': -0.8234674727692834, 'Vlen_freq': 1.166665233866222}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 1.582881953547104e-32, 'N1ratio-ArgsPreds': 4.685217924104467e-55, 'Fam_class': 0.01199021677031251, 'Nlen_freq': 2.6160414517557636e-06, 'Vlen_freq': 3.887777026105497e-13}</t>
+          <t>{'const': 1.4573778169596805e-32, 'N1ratio-ArgsPreds': 9.628970535920127e-53, 'Fam_class': 0.004067767869630182, 'Nlen_freq': 2.400104912121987e-07, 'Vlen_freq': 2.317916473415374e-14}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4414751325222649, 'Fam_class': -0.06903817348482645, 'Nlen_freq': -0.18807629279105129, 'Vlen_freq': 0.3047917757112661}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4304897915006256, 'Fam_class': -0.07893861219059453, 'Nlen_freq': -0.20647476440897208, 'Vlen_freq': 0.3200139086682237}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.43297137096243027), 'Fam_class': np.float64(-0.07315028764011519), 'Nlen_freq': np.float64(-0.1363524484569532), 'Vlen_freq': np.float64(0.20929550802411598)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.42438846770778), 'Fam_class': np.float64(-0.08360974930754651), 'Nlen_freq': np.float64(-0.1497423472402059), 'Vlen_freq': np.float64(0.21977011933115292)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.40823294109963243), 'Fam_class': np.float64(-0.06233776402780797), 'Nlen_freq': np.float64(-0.1169790950076564), 'Vlen_freq': np.float64(0.18191005282583103)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.3994693653614123), 'Fam_class': np.float64(-0.07151203101147975), 'Nlen_freq': np.float64(-0.12908267930643716), 'Vlen_freq': np.float64(0.19200707551582655)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(16.665413419885596), 'Fam_class': np.float64(0.3885996823986669), 'Nlen_freq': np.float64(1.3684108668810302), 'Vlen_freq': np.float64(3.309126731909664)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(15.957577386224953), 'Fam_class': np.float64(0.5113970579386842), 'Nlen_freq': np.float64(1.66623380969285), 'Vlen_freq': np.float64(3.6866717048140316)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.03463295125091903</v>
+        <v>0.03785357832382208</v>
       </c>
       <c r="V4" t="n">
-        <v>28.21601892960717</v>
+        <v>30.66589614276664</v>
       </c>
       <c r="W4" t="n">
-        <v>1.073095963301676e-12</v>
+        <v>1.040783494936282e-13</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_08_>75_lg_families_noLgArea_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_08_>75_lg_families_noLgArea_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2355842238404511</v>
+        <v>0.2353905796617167</v>
       </c>
       <c r="H2" t="n">
-        <v>363.662541775839</v>
+        <v>363.2715954217998</v>
       </c>
       <c r="I2" t="n">
-        <v>6.968483886006474e-71</v>
+        <v>8.095008422521239e-71</v>
       </c>
       <c r="J2" t="n">
-        <v>138.7796194903806</v>
+        <v>138.8147755746471</v>
       </c>
       <c r="K2" t="n">
         <v>181.5499153976311</v>
       </c>
       <c r="L2" t="n">
-        <v>42.7702959072505</v>
+        <v>42.73513982298402</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1176098470257463</v>
+        <v>0.1176396403174976</v>
       </c>
       <c r="N2" t="n">
         <v>0.1537255845873253</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.5682328519626636, 'N1ratio-ArgsPreds': -2.118622554728008}</t>
+          <t>{'const': 0.5677540716261412, 'N1ratio-ArgsPreds': -2.114660301017572}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 4.267556190895944e-115, 'N1ratio-ArgsPreds': 6.968483886004664e-71}</t>
+          <t>{'const': 4.817730324087699e-115, 'N1ratio-ArgsPreds': 8.095008422516971e-71}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.48537019257516306}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4851706706528301}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.48537019257516234)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.48517067065282893)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4853701925751624)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.48517067065282893)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(23.558422384045024)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(23.53905796617158)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2357097723163037</v>
+        <v>0.2355149141067605</v>
       </c>
       <c r="H3" t="n">
-        <v>181.8038563721716</v>
+        <v>181.6072601386547</v>
       </c>
       <c r="I3" t="n">
-        <v>1.516253387259223e-69</v>
+        <v>1.762120913249163e-69</v>
       </c>
       <c r="J3" t="n">
-        <v>138.7568261752113</v>
+        <v>138.7922026666684</v>
       </c>
       <c r="K3" t="n">
         <v>181.5499153976311</v>
       </c>
       <c r="L3" t="n">
-        <v>21.39654461120992</v>
+        <v>21.37885636548137</v>
       </c>
       <c r="M3" t="n">
-        <v>0.117690268172359</v>
+        <v>0.1177202736782599</v>
       </c>
       <c r="N3" t="n">
         <v>0.1537255845873253</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.5715863027053953, 'N1ratio-ArgsPreds': -2.1038747852921906, 'Fam_class': -0.00012087906762604605}</t>
+          <t>{'const': 0.5710916823429171, 'N1ratio-ArgsPreds': -2.0999928344401866, 'Fam_class': -0.00012030183078327232}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 3.187628831203141e-106, 'N1ratio-ArgsPreds': 5.885558436980357e-65, 'Fam_class': 0.6599584798021098}</t>
+          <t>{'const': 3.7268642444079006e-106, 'N1ratio-ArgsPreds': 6.843036583685959e-65, 'Fam_class': 0.6615439713746508}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.48199152199736595, 'Fam_class': -0.011703157297484928}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4818054849571873, 'Fam_class': -0.011647270916976241}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4668105918264926), 'Fam_class': np.float64(-0.012815657774598577)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4665969704847937), 'Fam_class': np.float64(-0.012751929643546411)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.46146851927307075), 'Fam_class': np.float64(-0.011204841625506699)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4612573425654359), 'Fam_class': np.float64(-0.011150535639306203)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(21.295319428008046), 'Fam_class': np.float64(0.012554847585268758)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.275833607052785), 'Fam_class': np.float64(0.012433444504343779)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.0001255484758526659</v>
+        <v>0.0001243344450437833</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1936720471736194</v>
+        <v>0.1917503865171438</v>
       </c>
       <c r="W3" t="n">
-        <v>0.659958479806684</v>
+        <v>0.6615439713788115</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2735633506401258</v>
+        <v>0.2734106281418196</v>
       </c>
       <c r="H4" t="n">
-        <v>110.8094091849427</v>
+        <v>110.7242693696231</v>
       </c>
       <c r="I4" t="n">
-        <v>3.344779760471392e-80</v>
+        <v>3.783147130560831e-80</v>
       </c>
       <c r="J4" t="n">
-        <v>131.8845122330238</v>
+        <v>131.9122389896706</v>
       </c>
       <c r="K4" t="n">
         <v>181.5499153976311</v>
       </c>
       <c r="L4" t="n">
-        <v>12.41635079115184</v>
+        <v>12.40941910199013</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1120514122625521</v>
+        <v>0.1120749694049878</v>
       </c>
       <c r="N4" t="n">
         <v>0.1537255845873253</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.5318082685667341, 'N1ratio-ArgsPreds': -1.8790716772582738, 'Fam_class': -0.0008153377416659804, 'Nlen_freq': -0.8234674727692834, 'Vlen_freq': 1.166665233866222}</t>
+          <t>{'const': 0.531959828384037, 'N1ratio-ArgsPreds': -1.874969851873204, 'Fam_class': -0.0008150001715501178, 'Nlen_freq': -0.8370231155795524, 'Vlen_freq': 1.1680375166609824}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 1.4573778169596805e-32, 'N1ratio-ArgsPreds': 9.628970535920127e-53, 'Fam_class': 0.004067767869630182, 'Nlen_freq': 2.400104912121987e-07, 'Vlen_freq': 2.317916473415374e-14}</t>
+          <t>{'const': 1.255562628886854e-32, 'N1ratio-ArgsPreds': 1.2010761532048796e-52, 'Fam_class': 0.004093402404030391, 'Nlen_freq': 2.1198002861080908e-07, 'Vlen_freq': 2.182108976104239e-14}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4304897915006256, 'Fam_class': -0.07893861219059453, 'Nlen_freq': -0.20647476440897208, 'Vlen_freq': 0.3200139086682237}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4301780196324785, 'Fam_class': -0.07890592964065055, 'Nlen_freq': -0.2074405731319884, 'Vlen_freq': 0.32043393900861067}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.42438846770778), 'Fam_class': np.float64(-0.08360974930754651), 'Nlen_freq': np.float64(-0.1497423472402059), 'Vlen_freq': np.float64(0.21977011933115292)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4240268362001594), 'Fam_class': np.float64(-0.08355217206626513), 'Nlen_freq': np.float64(-0.1504066719633418), 'Vlen_freq': np.float64(0.2199886022503376)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.3994693653614123), 'Fam_class': np.float64(-0.07151203101147975), 'Nlen_freq': np.float64(-0.12908267930643716), 'Vlen_freq': np.float64(0.19200707551582655)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.39909625510394797), 'Fam_class': np.float64(-0.071469950014525), 'Nlen_freq': np.float64(-0.12968220305679212), 'Vlen_freq': np.float64(0.19222786382519108)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(15.957577386224953), 'Fam_class': np.float64(0.5113970579386842), 'Nlen_freq': np.float64(1.66623380969285), 'Vlen_freq': np.float64(3.6866717048140316)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(15.927782083799553), 'Fam_class': np.float64(0.5107953755078702), 'Nlen_freq': np.float64(1.6817473789663064), 'Vlen_freq': np.float64(3.6951551630796207)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.03785357832382208</v>
+        <v>0.03789571403505909</v>
       </c>
       <c r="V4" t="n">
-        <v>30.66589614276664</v>
+        <v>30.69357820717645</v>
       </c>
       <c r="W4" t="n">
-        <v>1.040783494936282e-13</v>
+        <v>1.013757114319812e-13</v>
       </c>
     </row>
   </sheetData>
